--- a/calceulated_algoritm_tg_billing.xlsx
+++ b/calceulated_algoritm_tg_billing.xlsx
@@ -75,6 +75,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -154,8 +157,8 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -444,9 +447,9 @@
     <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="40" style="8" customWidth="1"/>
+    <col min="9" max="9" width="40" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -494,14 +497,14 @@
       <c r="E2" s="5">
         <v>45959</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="4">
         <v>0.62083333333333335</v>
       </c>
       <c r="H2" s="5">
         <v>45959</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -519,14 +522,14 @@
       <c r="E3" s="5">
         <v>45959</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="4">
         <v>0.6694444444444444</v>
       </c>
       <c r="H3" s="5">
         <v>45959</v>
       </c>
-      <c r="I3" s="7"/>
+      <c r="I3" s="8"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -544,14 +547,14 @@
       <c r="E4" s="5">
         <v>45960</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
       <c r="G4" s="4">
         <v>0.56874999999999998</v>
       </c>
       <c r="H4" s="5">
         <v>45960</v>
       </c>
-      <c r="I4" s="7"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -569,14 +572,14 @@
       <c r="E5" s="5">
         <v>45959</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="8"/>
       <c r="G5" s="4">
         <v>0.67152777777777783</v>
       </c>
       <c r="H5" s="5">
         <v>45959</v>
       </c>
-      <c r="I5" s="7"/>
+      <c r="I5" s="8"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -594,14 +597,14 @@
       <c r="E6" s="5">
         <v>45961</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="4">
         <v>0.90208333333333324</v>
       </c>
       <c r="H6" s="5">
         <v>45962</v>
       </c>
-      <c r="I6" s="7"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -619,14 +622,14 @@
       <c r="E7" s="5">
         <v>45960</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="4">
         <v>0.70347222222222217</v>
       </c>
       <c r="H7" s="5">
         <v>45960</v>
       </c>
-      <c r="I7" s="7"/>
+      <c r="I7" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/calceulated_algoritm_tg_billing.xlsx
+++ b/calceulated_algoritm_tg_billing.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\bot_excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\bot_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9DD00B-EA69-4367-8763-A9399CF68302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12696" windowHeight="5712"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -50,9 +51,6 @@
     <t>Время обработки (D2-B2)</t>
   </si>
   <si>
-    <t>Время с момента передачи тикета до взятия его обратно в работу мотрудниками ЦКП (G2-B2)</t>
-  </si>
-  <si>
     <t>61-227-715</t>
   </si>
   <si>
@@ -69,14 +67,17 @@
   </si>
   <si>
     <t>61-257-789</t>
+  </si>
+  <si>
+    <t>Время с момента передачи тикета до взятия его обратно в работу сотрудниками ЦКП (G2-B2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -158,7 +159,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -438,21 +439,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="40" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -478,12 +479,12 @@
         <v>6</v>
       </c>
       <c r="I1" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="B2" s="4">
         <v>0.60138888888888886</v>
@@ -506,9 +507,9 @@
       </c>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>0.61875000000000002</v>
@@ -531,9 +532,9 @@
       </c>
       <c r="I3" s="8"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4">
         <v>0.8847222222222223</v>
@@ -556,9 +557,9 @@
       </c>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>0.63263888888888886</v>
@@ -581,9 +582,9 @@
       </c>
       <c r="I5" s="8"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4">
         <v>0.7055555555555556</v>
@@ -606,9 +607,9 @@
       </c>
       <c r="I6" s="8"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="4">
         <v>0.56527777777777777</v>
